--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="L2" t="n">
-        <v>11.79</v>
+        <v>13.41</v>
       </c>
       <c r="M2" t="n">
-        <v>11.59</v>
+        <v>11.61</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="G3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="I3" t="n">
-        <v>60.9</v>
+        <v>74</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,66 +686,66 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.95</v>
+        <v>-1.41</v>
       </c>
       <c r="L3" t="n">
-        <v>65.95999999999999</v>
+        <v>30.51</v>
       </c>
       <c r="M3" t="n">
-        <v>29.74</v>
+        <v>22.76</v>
       </c>
       <c r="N3" t="n">
-        <v>-20.33</v>
+        <v>-15.59</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>74.09999999999999</v>
+        <v>61</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-3.15</v>
+        <v>5.98</v>
       </c>
       <c r="L4" t="n">
-        <v>30.17</v>
+        <v>67.33</v>
       </c>
       <c r="M4" t="n">
-        <v>22.73</v>
+        <v>29.69</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.59</v>
+        <v>-20.33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.8</v>
+        <v>81.8</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I5" t="n">
         <v>89.40000000000001</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13.49</v>
+        <v>10.2</v>
       </c>
       <c r="L5" t="n">
-        <v>5.51</v>
+        <v>6.77</v>
       </c>
       <c r="M5" t="n">
-        <v>14.42</v>
+        <v>14.39</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -970,30 +970,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.8</v>
+        <v>78.3</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>77.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="I6" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-11.94</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>47.82</v>
+        <v>50.75</v>
       </c>
       <c r="M6" t="n">
-        <v>38.9</v>
+        <v>38.85</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>56.4</v>
+        <v>58.1</v>
       </c>
       <c r="I7" t="n">
         <v>95.59999999999999</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.33</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.75</v>
+        <v>-1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>11.41</v>
+        <v>11.4</v>
       </c>
       <c r="N7" t="n">
         <v>-6.3</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>68.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>59.5</v>
+        <v>63.1</v>
       </c>
       <c r="I8" t="n">
         <v>77.2</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.62</v>
+        <v>5.92</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.77</v>
+        <v>-2.84</v>
       </c>
       <c r="M8" t="n">
-        <v>17.98</v>
+        <v>17.94</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>65.3</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>51.7</v>
+        <v>50.8</v>
       </c>
       <c r="I9" t="n">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-0.19</v>
+        <v>0.91</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.699999999999999</v>
+        <v>-11.79</v>
       </c>
       <c r="M9" t="n">
-        <v>26.33</v>
+        <v>26.29</v>
       </c>
       <c r="N9" t="n">
         <v>-25.29</v>
@@ -1404,16 +1404,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.3</v>
+        <v>60.8</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>47</v>
+        <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-0.05</v>
+        <v>-0.28</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.67</v>
+        <v>-13.18</v>
       </c>
       <c r="M10" t="n">
-        <v>25.78</v>
+        <v>25.66</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,30 +1598,30 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>57.1</v>
+        <v>52.4</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>54.9</v>
+        <v>41.2</v>
       </c>
       <c r="I12" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-2.42</v>
+        <v>-3.11</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.76</v>
+        <v>-18.62</v>
       </c>
       <c r="M12" t="n">
-        <v>46.08</v>
+        <v>46.22</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46.9</v>
+        <v>48.2</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>18.8</v>
+        <v>22.6</v>
       </c>
       <c r="I13" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-24.47</v>
+        <v>-22.72</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.56</v>
+        <v>-0.14</v>
       </c>
       <c r="M13" t="n">
-        <v>27.68</v>
+        <v>27.6</v>
       </c>
       <c r="N13" t="n">
         <v>-25.99</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.25</v>
+        <v>2.68</v>
       </c>
       <c r="L2" t="n">
-        <v>13.41</v>
+        <v>12.35</v>
       </c>
       <c r="M2" t="n">
         <v>11.61</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>74</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-1.41</v>
+        <v>-1.97</v>
       </c>
       <c r="L3" t="n">
-        <v>30.51</v>
+        <v>31.76</v>
       </c>
       <c r="M3" t="n">
-        <v>22.76</v>
+        <v>22.75</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81.8</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>83</v>
+        <v>86.7</v>
       </c>
       <c r="I5" t="n">
         <v>89.40000000000001</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10.2</v>
+        <v>13.87</v>
       </c>
       <c r="L5" t="n">
-        <v>6.77</v>
+        <v>5.86</v>
       </c>
       <c r="M5" t="n">
-        <v>14.39</v>
+        <v>14.41</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -970,30 +970,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>78.3</v>
+        <v>77.5</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>81.7</v>
+        <v>79.2</v>
       </c>
       <c r="I6" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-9.880000000000001</v>
+        <v>-11.06</v>
       </c>
       <c r="L6" t="n">
-        <v>50.75</v>
+        <v>49.28</v>
       </c>
       <c r="M6" t="n">
-        <v>38.85</v>
+        <v>38.88</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.5</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>58.1</v>
+        <v>56.7</v>
       </c>
       <c r="I7" t="n">
         <v>95.59999999999999</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.82</v>
+        <v>-0.18</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.28</v>
+        <v>-1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>11.4</v>
+        <v>11.42</v>
       </c>
       <c r="N7" t="n">
         <v>-6.3</v>
@@ -1404,30 +1404,30 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.8</v>
+        <v>64.7</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>48.4</v>
+        <v>59.7</v>
       </c>
       <c r="I10" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-0.28</v>
+        <v>2.61</v>
       </c>
       <c r="L10" t="n">
-        <v>-13.18</v>
+        <v>-13.43</v>
       </c>
       <c r="M10" t="n">
-        <v>25.66</v>
+        <v>25.59</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48.2</v>
+        <v>47.3</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>22.6</v>
+        <v>20</v>
       </c>
       <c r="I13" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-22.72</v>
+        <v>-23.92</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.14</v>
+        <v>-1.84</v>
       </c>
       <c r="M13" t="n">
-        <v>27.6</v>
+        <v>27.64</v>
       </c>
       <c r="N13" t="n">
         <v>-25.99</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.3</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.68</v>
+        <v>1.72</v>
       </c>
       <c r="L2" t="n">
-        <v>12.35</v>
+        <v>12.83</v>
       </c>
       <c r="M2" t="n">
-        <v>11.61</v>
+        <v>11.65</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>85.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="I3" t="n">
         <v>74</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-1.97</v>
+        <v>-1.84</v>
       </c>
       <c r="L3" t="n">
-        <v>31.76</v>
+        <v>29.95</v>
       </c>
       <c r="M3" t="n">
-        <v>22.75</v>
+        <v>22.8</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>61</v>
+        <v>60.6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.98</v>
+        <v>4.52</v>
       </c>
       <c r="L4" t="n">
-        <v>67.33</v>
+        <v>58.8</v>
       </c>
       <c r="M4" t="n">
-        <v>29.69</v>
+        <v>29.96</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>82.3</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>86.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>89.40000000000001</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13.87</v>
+        <v>11.04</v>
       </c>
       <c r="L5" t="n">
-        <v>5.86</v>
+        <v>7.58</v>
       </c>
       <c r="M5" t="n">
-        <v>14.41</v>
+        <v>14.38</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -990,7 +990,7 @@
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>46.1</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-11.06</v>
+        <v>-10.85</v>
       </c>
       <c r="L6" t="n">
-        <v>49.28</v>
+        <v>49.13</v>
       </c>
       <c r="M6" t="n">
-        <v>38.88</v>
+        <v>38.91</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>72.2</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>56.7</v>
+        <v>57.4</v>
       </c>
       <c r="I7" t="n">
-        <v>95.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.18</v>
+        <v>0.44</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.6</v>
+        <v>-1.65</v>
       </c>
       <c r="M7" t="n">
         <v>11.42</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.3</v>
+        <v>-6.56</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>69.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>63.1</v>
+        <v>64</v>
       </c>
       <c r="I8" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5.92</v>
+        <v>4.75</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.84</v>
+        <v>0.39</v>
       </c>
       <c r="M8" t="n">
-        <v>17.94</v>
+        <v>17.88</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>59.9</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>50.8</v>
+        <v>36</v>
       </c>
       <c r="I9" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.91</v>
+        <v>-2.9</v>
       </c>
       <c r="L9" t="n">
-        <v>-11.79</v>
+        <v>-15.01</v>
       </c>
       <c r="M9" t="n">
-        <v>26.29</v>
+        <v>26.53</v>
       </c>
       <c r="N9" t="n">
         <v>-25.29</v>
@@ -1390,44 +1390,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>64.7</v>
+        <v>59.6</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>59.7</v>
+        <v>45</v>
       </c>
       <c r="I10" t="n">
-        <v>65.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2.61</v>
+        <v>-2.17</v>
       </c>
       <c r="L10" t="n">
-        <v>-13.43</v>
+        <v>-14.83</v>
       </c>
       <c r="M10" t="n">
-        <v>25.59</v>
+        <v>25.9</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.4</v>
+        <v>51.3</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>41.2</v>
+        <v>38</v>
       </c>
       <c r="I12" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-3.11</v>
+        <v>-6.22</v>
       </c>
       <c r="L12" t="n">
-        <v>-18.62</v>
+        <v>-17.92</v>
       </c>
       <c r="M12" t="n">
-        <v>46.22</v>
+        <v>46.41</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="I13" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-23.92</v>
+        <v>-23.75</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.84</v>
+        <v>-1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>27.64</v>
+        <v>27.66</v>
       </c>
       <c r="N13" t="n">
-        <v>-25.99</v>
+        <v>-26.1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>88.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="L2" t="n">
-        <v>12.83</v>
+        <v>11.25</v>
       </c>
       <c r="M2" t="n">
-        <v>11.65</v>
+        <v>11.59</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>84.8</v>
+        <v>85.7</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-1.84</v>
+        <v>0.39</v>
       </c>
       <c r="L3" t="n">
-        <v>29.95</v>
+        <v>27.44</v>
       </c>
       <c r="M3" t="n">
-        <v>22.8</v>
+        <v>22.71</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,21 +783,21 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>60.6</v>
+        <v>60.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="L4" t="n">
-        <v>58.8</v>
+        <v>57.73</v>
       </c>
       <c r="M4" t="n">
-        <v>29.96</v>
+        <v>30.07</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.3</v>
+        <v>81.5</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>84.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="I5" t="n">
         <v>89.40000000000001</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.04</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>7.58</v>
+        <v>7.38</v>
       </c>
       <c r="M5" t="n">
-        <v>14.38</v>
+        <v>14.44</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -970,30 +970,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>79.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I6" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-10.85</v>
+        <v>-6.95</v>
       </c>
       <c r="L6" t="n">
-        <v>49.13</v>
+        <v>45.86</v>
       </c>
       <c r="M6" t="n">
-        <v>38.91</v>
+        <v>38.82</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.2</v>
+        <v>71.2</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>57.4</v>
+        <v>54.5</v>
       </c>
       <c r="I7" t="n">
         <v>95.40000000000001</v>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.44</v>
+        <v>-1.82</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.65</v>
+        <v>-1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>11.42</v>
+        <v>11.41</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.56</v>
+        <v>-6.58</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>64</v>
+        <v>63.6</v>
       </c>
       <c r="I8" t="n">
         <v>77.3</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="L8" t="n">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>17.88</v>
+        <v>17.91</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.9</v>
+        <v>60.2</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>36</v>
+        <v>46.7</v>
       </c>
       <c r="I9" t="n">
-        <v>62</v>
+        <v>64.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.9</v>
+        <v>-0.48</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.01</v>
+        <v>-15.35</v>
       </c>
       <c r="M9" t="n">
-        <v>26.53</v>
+        <v>25.75</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>34.9</v>
       </c>
       <c r="I10" t="n">
-        <v>64.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-2.17</v>
+        <v>-3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-14.83</v>
+        <v>-15.54</v>
       </c>
       <c r="M10" t="n">
-        <v>25.9</v>
+        <v>26.65</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>38</v>
+        <v>35.7</v>
       </c>
       <c r="I12" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-6.22</v>
+        <v>-7.46</v>
       </c>
       <c r="L12" t="n">
-        <v>-17.92</v>
+        <v>-19.01</v>
       </c>
       <c r="M12" t="n">
-        <v>46.41</v>
+        <v>46.5</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>20.5</v>
+        <v>22.1</v>
       </c>
       <c r="I13" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-23.75</v>
+        <v>-21.07</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.46</v>
+        <v>-3.7</v>
       </c>
       <c r="M13" t="n">
-        <v>27.66</v>
+        <v>27.63</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.1</v>
+        <v>-26.44</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>76.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="L2" t="n">
-        <v>11.25</v>
+        <v>11.41</v>
       </c>
       <c r="M2" t="n">
         <v>11.59</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>85.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>74.09999999999999</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.39</v>
+        <v>0.02</v>
       </c>
       <c r="L3" t="n">
-        <v>27.44</v>
+        <v>26.97</v>
       </c>
       <c r="M3" t="n">
-        <v>22.71</v>
+        <v>22.72</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.3</v>
+        <v>82.3</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I4" t="n">
-        <v>60.5</v>
+        <v>59.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.82</v>
+        <v>1.38</v>
       </c>
       <c r="L4" t="n">
-        <v>57.73</v>
+        <v>54.02</v>
       </c>
       <c r="M4" t="n">
-        <v>30.07</v>
+        <v>30.48</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81.5</v>
+        <v>82</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>82.2</v>
+        <v>83.7</v>
       </c>
       <c r="I5" t="n">
-        <v>89.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.210000000000001</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>7.38</v>
+        <v>8.17</v>
       </c>
       <c r="M5" t="n">
-        <v>14.44</v>
+        <v>14.52</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>81.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>46.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-6.95</v>
+        <v>-7.26</v>
       </c>
       <c r="L6" t="n">
-        <v>45.86</v>
+        <v>45.38</v>
       </c>
       <c r="M6" t="n">
-        <v>38.82</v>
+        <v>38.83</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>54.5</v>
+        <v>53</v>
       </c>
       <c r="I7" t="n">
-        <v>95.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.82</v>
+        <v>-2.61</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.83</v>
+        <v>-2.62</v>
       </c>
       <c r="M7" t="n">
-        <v>11.41</v>
+        <v>11.45</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.58</v>
+        <v>-7.33</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>63.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>77.3</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.55</v>
+        <v>4.84</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="M8" t="n">
         <v>17.91</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.2</v>
+        <v>60.8</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>46.7</v>
+        <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-0.48</v>
+        <v>0.49</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.35</v>
+        <v>-14.52</v>
       </c>
       <c r="M9" t="n">
-        <v>25.75</v>
+        <v>25.7</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.5</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34.9</v>
+        <v>33.5</v>
       </c>
       <c r="I10" t="n">
-        <v>61.8</v>
+        <v>61.6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-3.5</v>
+        <v>-4.29</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.54</v>
+        <v>-16.23</v>
       </c>
       <c r="M10" t="n">
-        <v>26.65</v>
+        <v>26.78</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.5</v>
+        <v>51.1</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>35.7</v>
+        <v>37.3</v>
       </c>
       <c r="I12" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.46</v>
+        <v>-6.62</v>
       </c>
       <c r="L12" t="n">
-        <v>-19.01</v>
+        <v>-18.28</v>
       </c>
       <c r="M12" t="n">
-        <v>46.5</v>
+        <v>46.41</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="I13" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-21.07</v>
+        <v>-21.21</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.7</v>
+        <v>-3.87</v>
       </c>
       <c r="M13" t="n">
         <v>27.63</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.44</v>
+        <v>-26.57</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>76.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="L2" t="n">
-        <v>11.41</v>
+        <v>11.73</v>
       </c>
       <c r="M2" t="n">
         <v>11.59</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>84.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>74.09999999999999</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>26.97</v>
+        <v>27.98</v>
       </c>
       <c r="M3" t="n">
-        <v>22.72</v>
+        <v>22.7</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>97.5</v>
+        <v>97.7</v>
       </c>
       <c r="I4" t="n">
         <v>59.9</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="L4" t="n">
-        <v>54.02</v>
+        <v>54.16</v>
       </c>
       <c r="M4" t="n">
-        <v>30.48</v>
+        <v>30.46</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82</v>
+        <v>81.7</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>83.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>9.58</v>
       </c>
       <c r="L5" t="n">
-        <v>8.17</v>
+        <v>7.76</v>
       </c>
       <c r="M5" t="n">
-        <v>14.52</v>
+        <v>14.48</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>78.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>81.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-7.26</v>
+        <v>-6.03</v>
       </c>
       <c r="L6" t="n">
-        <v>45.38</v>
+        <v>47.31</v>
       </c>
       <c r="M6" t="n">
-        <v>38.83</v>
+        <v>38.78</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>70.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>53</v>
+        <v>54.3</v>
       </c>
       <c r="I7" t="n">
-        <v>94.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.61</v>
+        <v>-1.94</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.62</v>
+        <v>-1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>11.45</v>
+        <v>11.41</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.33</v>
+        <v>-6.69</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>64.09999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="I8" t="n">
         <v>77.3</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.84</v>
+        <v>4.55</v>
       </c>
       <c r="L8" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
         <v>17.91</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.8</v>
+        <v>60.5</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>48.4</v>
+        <v>47.7</v>
       </c>
       <c r="I9" t="n">
         <v>64.90000000000001</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.49</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-14.52</v>
+        <v>-14.87</v>
       </c>
       <c r="M9" t="n">
-        <v>25.7</v>
+        <v>25.71</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>58.6</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.5</v>
+        <v>32.6</v>
       </c>
       <c r="I10" t="n">
-        <v>61.6</v>
+        <v>61.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.29</v>
+        <v>-4.78</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.23</v>
+        <v>-16.66</v>
       </c>
       <c r="M10" t="n">
-        <v>26.78</v>
+        <v>26.87</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.1</v>
+        <v>50.7</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>37.3</v>
+        <v>36.2</v>
       </c>
       <c r="I12" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-6.62</v>
+        <v>-7.22</v>
       </c>
       <c r="L12" t="n">
-        <v>-18.28</v>
+        <v>-18.8</v>
       </c>
       <c r="M12" t="n">
-        <v>46.41</v>
+        <v>46.47</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="I13" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-21.21</v>
+        <v>-21.06</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.87</v>
+        <v>-3.69</v>
       </c>
       <c r="M13" t="n">
         <v>27.63</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.57</v>
+        <v>-26.43</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.75</v>
+        <v>4.02</v>
       </c>
       <c r="L2" t="n">
-        <v>11.73</v>
+        <v>13.29</v>
       </c>
       <c r="M2" t="n">
-        <v>11.59</v>
+        <v>11.6</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>86.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>74.09999999999999</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.61</v>
       </c>
       <c r="L3" t="n">
-        <v>27.98</v>
+        <v>28.1</v>
       </c>
       <c r="M3" t="n">
-        <v>22.7</v>
+        <v>22.68</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>59.9</v>
+        <v>60.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.47</v>
+        <v>5.32</v>
       </c>
       <c r="L4" t="n">
-        <v>54.16</v>
+        <v>52.54</v>
       </c>
       <c r="M4" t="n">
-        <v>30.46</v>
+        <v>30.06</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>82.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="I5" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.58</v>
+        <v>10.22</v>
       </c>
       <c r="L5" t="n">
-        <v>7.76</v>
+        <v>9.34</v>
       </c>
       <c r="M5" t="n">
-        <v>14.48</v>
+        <v>14.43</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -970,27 +970,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>83.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>46.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-6.03</v>
+        <v>-8.73</v>
       </c>
       <c r="L6" t="n">
-        <v>47.31</v>
+        <v>45.85</v>
       </c>
       <c r="M6" t="n">
-        <v>38.78</v>
+        <v>38.8</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>54.3</v>
+        <v>56.7</v>
       </c>
       <c r="I7" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.94</v>
+        <v>-0.57</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.95</v>
+        <v>-0.93</v>
       </c>
       <c r="M7" t="n">
-        <v>11.41</v>
+        <v>11.42</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.69</v>
+        <v>-6.56</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>63.6</v>
+        <v>64</v>
       </c>
       <c r="I8" t="n">
         <v>77.3</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.55</v>
+        <v>5.53</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>-0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>17.91</v>
+        <v>17.89</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.5</v>
+        <v>62.5</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>47.7</v>
+        <v>53.7</v>
       </c>
       <c r="I9" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.13</v>
       </c>
       <c r="L9" t="n">
-        <v>-14.87</v>
+        <v>-11.5</v>
       </c>
       <c r="M9" t="n">
-        <v>25.71</v>
+        <v>25.85</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.6</v>
+        <v>59.7</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>32.6</v>
+        <v>35.6</v>
       </c>
       <c r="I10" t="n">
-        <v>61.5</v>
+        <v>61.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.78</v>
+        <v>-2.34</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.66</v>
+        <v>-16.6</v>
       </c>
       <c r="M10" t="n">
-        <v>26.87</v>
+        <v>26.61</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.7</v>
+        <v>55.8</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>36.2</v>
+        <v>51.2</v>
       </c>
       <c r="I12" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.22</v>
+        <v>2.75</v>
       </c>
       <c r="L12" t="n">
-        <v>-18.8</v>
+        <v>-14.47</v>
       </c>
       <c r="M12" t="n">
-        <v>46.47</v>
+        <v>46.4</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>22.1</v>
+        <v>27.8</v>
       </c>
       <c r="I13" t="n">
-        <v>59.6</v>
+        <v>59.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-21.06</v>
+        <v>-17.82</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.69</v>
+        <v>-1.12</v>
       </c>
       <c r="M13" t="n">
-        <v>27.63</v>
+        <v>27.65</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.43</v>
+        <v>-26.1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.02</v>
+        <v>5.25</v>
       </c>
       <c r="L2" t="n">
-        <v>13.29</v>
+        <v>14.67</v>
       </c>
       <c r="M2" t="n">
-        <v>11.6</v>
+        <v>11.57</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>87.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="I3" t="n">
         <v>74.09999999999999</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.61</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>28.1</v>
+        <v>30.42</v>
       </c>
       <c r="M3" t="n">
-        <v>22.68</v>
+        <v>22.69</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.32</v>
+        <v>6.84</v>
       </c>
       <c r="L4" t="n">
-        <v>52.54</v>
+        <v>49.87</v>
       </c>
       <c r="M4" t="n">
-        <v>30.06</v>
+        <v>30.17</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,83 +879,83 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="G5" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>84.8</v>
+        <v>93.2</v>
       </c>
       <c r="I5" t="n">
-        <v>89.40000000000001</v>
+        <v>46.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10.22</v>
+        <v>-2.56</v>
       </c>
       <c r="L5" t="n">
-        <v>9.34</v>
+        <v>54.73</v>
       </c>
       <c r="M5" t="n">
-        <v>14.43</v>
+        <v>38.82</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.32</v>
+        <v>-23.17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -965,102 +965,102 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>79.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="I6" t="n">
-        <v>46.3</v>
+        <v>89.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-8.73</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>45.85</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>38.8</v>
+        <v>14.45</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.32</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
         <v>56.7</v>
       </c>
       <c r="I7" t="n">
-        <v>95.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.57</v>
+        <v>-0.66</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.93</v>
+        <v>-0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>11.42</v>
+        <v>11.41</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.56</v>
+        <v>-6.69</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70.2</v>
+        <v>70.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>64</v>
+        <v>65.5</v>
       </c>
       <c r="I8" t="n">
         <v>77.3</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5.53</v>
+        <v>6.37</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.86</v>
+        <v>-0.23</v>
       </c>
       <c r="M8" t="n">
         <v>17.89</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>62.5</v>
+        <v>62.2</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>53.7</v>
+        <v>52.6</v>
       </c>
       <c r="I9" t="n">
-        <v>64.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.13</v>
+        <v>3.27</v>
       </c>
       <c r="L9" t="n">
-        <v>-11.5</v>
+        <v>-13.25</v>
       </c>
       <c r="M9" t="n">
-        <v>25.85</v>
+        <v>25.72</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.7</v>
+        <v>60.7</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>35.6</v>
+        <v>38.5</v>
       </c>
       <c r="I10" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-2.34</v>
+        <v>-1.24</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.6</v>
+        <v>-14.26</v>
       </c>
       <c r="M10" t="n">
-        <v>26.61</v>
+        <v>26.58</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.8</v>
+        <v>56.8</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>51.2</v>
+        <v>54.2</v>
       </c>
       <c r="I12" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.47</v>
+        <v>-11.88</v>
       </c>
       <c r="M12" t="n">
-        <v>46.4</v>
+        <v>46.46</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>51.8</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>27.8</v>
+        <v>33.2</v>
       </c>
       <c r="I13" t="n">
-        <v>59.8</v>
+        <v>59.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-17.82</v>
+        <v>-13.92</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.12</v>
+        <v>-0.17</v>
       </c>
       <c r="M13" t="n">
-        <v>27.65</v>
+        <v>27.74</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.1</v>
+        <v>-26.43</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>14.67</v>
+        <v>13.42</v>
       </c>
       <c r="M2" t="n">
-        <v>11.57</v>
+        <v>11.55</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>6.34</v>
       </c>
       <c r="L3" t="n">
-        <v>30.42</v>
+        <v>28.77</v>
       </c>
       <c r="M3" t="n">
-        <v>22.69</v>
+        <v>22.63</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>60.3</v>
+        <v>60.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6.84</v>
+        <v>10.68</v>
       </c>
       <c r="L4" t="n">
-        <v>49.87</v>
+        <v>45.91</v>
       </c>
       <c r="M4" t="n">
-        <v>30.17</v>
+        <v>30.12</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,83 +879,83 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.2</v>
+        <v>81.3</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>93.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>46.2</v>
+        <v>89.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-2.56</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>54.73</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>38.82</v>
+        <v>14.46</v>
       </c>
       <c r="N5" t="n">
-        <v>-23.17</v>
+        <v>-10.32</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,83 +984,83 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="G6" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>83.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>89.3</v>
+        <v>46.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>9.359999999999999</v>
+        <v>-3.54</v>
       </c>
       <c r="L6" t="n">
-        <v>9.390000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="M6" t="n">
-        <v>14.45</v>
+        <v>38.88</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.32</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>56.7</v>
+        <v>55.1</v>
       </c>
       <c r="I7" t="n">
         <v>95.3</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.66</v>
+        <v>-1.87</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7</v>
+        <v>-0.88</v>
       </c>
       <c r="M7" t="n">
-        <v>11.41</v>
+        <v>11.39</v>
       </c>
       <c r="N7" t="n">
         <v>-6.69</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70.7</v>
+        <v>67.2</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>65.5</v>
+        <v>55.2</v>
       </c>
       <c r="I8" t="n">
         <v>77.3</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6.37</v>
+        <v>4.47</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>17.89</v>
+        <v>17.92</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>62.2</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>52.6</v>
+        <v>55.1</v>
       </c>
       <c r="I9" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.27</v>
+        <v>6.63</v>
       </c>
       <c r="L9" t="n">
-        <v>-13.25</v>
+        <v>-15.45</v>
       </c>
       <c r="M9" t="n">
-        <v>25.72</v>
+        <v>25.88</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1381,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.7</v>
+        <v>60.6</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H10" t="n">
-        <v>38.5</v>
+        <v>65.3</v>
       </c>
       <c r="I10" t="n">
-        <v>61.9</v>
+        <v>26.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,46 +1417,46 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.24</v>
+        <v>11.6</v>
       </c>
       <c r="L10" t="n">
-        <v>-14.26</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>26.58</v>
+        <v>46.3</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.29</v>
+        <v>-36.07</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>LMT|RTX|BA.L</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>
@@ -1486,90 +1486,102 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Obbligazionario Globale</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>57.7</v>
+        <v>59.9</v>
       </c>
       <c r="G11" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>36.1</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>61.9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dati limitati</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Debole o laterale</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-18.08</v>
+      </c>
+      <c r="M11" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-25.29</v>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>ETF obbligazionario</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>EUNA.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ETF global aggregate bond hedged/unhedged</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>9-35%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Lungo periodo</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Rischio tassi cambio e duration</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Da allineare a orizzonte e consulenza Fineco</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1591,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Obbligazionario Globale</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,83 +1610,71 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56.8</v>
+        <v>57.7</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H12" t="n">
-        <v>54.2</v>
+        <v>50</v>
       </c>
       <c r="I12" t="n">
-        <v>26.5</v>
+        <v>50</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-11.88</v>
-      </c>
-      <c r="M12" t="n">
-        <v>46.46</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-36.07</v>
-      </c>
+          <t>Dati limitati</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF obbligazionario</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>EUNA.MI</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
-        </is>
-      </c>
+          <t>ETF global aggregate bond hedged/unhedged</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>9-35%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Lungo periodo</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Rischio tassi cambio e duration</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Da allineare a orizzonte e consulenza Fineco</t>
         </is>
       </c>
     </row>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="I13" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-13.92</v>
+        <v>-12.09</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.17</v>
+        <v>-3.45</v>
       </c>
       <c r="M13" t="n">
-        <v>27.74</v>
+        <v>27.67</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="L2" t="n">
-        <v>13.42</v>
+        <v>13.36</v>
       </c>
       <c r="M2" t="n">
         <v>11.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.34</v>
+        <v>6.41</v>
       </c>
       <c r="L3" t="n">
-        <v>28.77</v>
+        <v>28.86</v>
       </c>
       <c r="M3" t="n">
         <v>22.63</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.68</v>
+        <v>11.25</v>
       </c>
       <c r="L4" t="n">
-        <v>45.91</v>
+        <v>46.67</v>
       </c>
       <c r="M4" t="n">
-        <v>30.12</v>
+        <v>30.11</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,83 +879,83 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>81.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="I5" t="n">
-        <v>89.3</v>
+        <v>46.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.039999999999999</v>
+        <v>-3.13</v>
       </c>
       <c r="L5" t="n">
-        <v>8.550000000000001</v>
+        <v>50.84</v>
       </c>
       <c r="M5" t="n">
-        <v>14.46</v>
+        <v>38.89</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.32</v>
+        <v>-23.17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,83 +984,83 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>88.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I6" t="n">
-        <v>46.2</v>
+        <v>89.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-3.54</v>
+        <v>7.8</v>
       </c>
       <c r="L6" t="n">
-        <v>50.2</v>
+        <v>8.31</v>
       </c>
       <c r="M6" t="n">
-        <v>38.88</v>
+        <v>14.47</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.32</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>55.1</v>
+        <v>54.8</v>
       </c>
       <c r="I7" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.87</v>
+        <v>-2.03</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.88</v>
+        <v>-1.05</v>
       </c>
       <c r="M7" t="n">
         <v>11.39</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.69</v>
+        <v>-6.82</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>55.2</v>
+        <v>55.1</v>
       </c>
       <c r="I8" t="n">
         <v>77.3</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.47</v>
+        <v>4.41</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.27</v>
+        <v>-0.33</v>
       </c>
       <c r="M8" t="n">
         <v>17.92</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>63.3</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>55.1</v>
+        <v>56</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6.63</v>
+        <v>7.12</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.45</v>
+        <v>-15.06</v>
       </c>
       <c r="M9" t="n">
-        <v>25.88</v>
+        <v>25.86</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
       </c>
       <c r="H10" t="n">
-        <v>65.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>26.7</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>11.6</v>
+        <v>11.79</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>46.3</v>
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>59.9</v>
+        <v>59.7</v>
       </c>
       <c r="G11" t="n">
         <v>76</v>
       </c>
       <c r="H11" t="n">
-        <v>36.1</v>
+        <v>35.5</v>
       </c>
       <c r="I11" t="n">
         <v>61.9</v>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-1</v>
+        <v>-1.37</v>
       </c>
       <c r="L11" t="n">
-        <v>-18.08</v>
+        <v>-18.38</v>
       </c>
       <c r="M11" t="n">
-        <v>26.54</v>
+        <v>26.55</v>
       </c>
       <c r="N11" t="n">
         <v>-25.29</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>33.1</v>
+        <v>33.4</v>
       </c>
       <c r="I13" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.09</v>
+        <v>-11.92</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.45</v>
+        <v>-3.26</v>
       </c>
       <c r="M13" t="n">
-        <v>27.67</v>
+        <v>27.68</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="L2" t="n">
-        <v>13.36</v>
+        <v>13.35</v>
       </c>
       <c r="M2" t="n">
         <v>11.55</v>
@@ -675,7 +675,7 @@
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>93.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.41</v>
+        <v>6.51</v>
       </c>
       <c r="L3" t="n">
-        <v>28.86</v>
+        <v>28.98</v>
       </c>
       <c r="M3" t="n">
         <v>22.63</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.25</v>
+        <v>10.37</v>
       </c>
       <c r="L4" t="n">
-        <v>46.67</v>
+        <v>45.52</v>
       </c>
       <c r="M4" t="n">
-        <v>30.11</v>
+        <v>30.12</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>89.8</v>
+        <v>91.3</v>
       </c>
       <c r="I5" t="n">
         <v>46.1</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-3.13</v>
+        <v>-2.48</v>
       </c>
       <c r="L5" t="n">
-        <v>50.84</v>
+        <v>51.84</v>
       </c>
       <c r="M5" t="n">
-        <v>38.89</v>
+        <v>38.92</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>81.2</v>
+        <v>80.2</v>
       </c>
       <c r="I6" t="n">
         <v>89.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7.8</v>
+        <v>7.28</v>
       </c>
       <c r="L6" t="n">
-        <v>8.31</v>
+        <v>7.79</v>
       </c>
       <c r="M6" t="n">
-        <v>14.47</v>
+        <v>14.52</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>54.8</v>
+        <v>55.1</v>
       </c>
       <c r="I7" t="n">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.03</v>
+        <v>-1.91</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.05</v>
+        <v>-0.93</v>
       </c>
       <c r="M7" t="n">
         <v>11.39</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.82</v>
+        <v>-6.71</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>55.1</v>
+        <v>54.9</v>
       </c>
       <c r="I8" t="n">
         <v>77.3</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.41</v>
+        <v>4.32</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.33</v>
+        <v>-0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>17.92</v>
+        <v>17.93</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1305,7 +1305,7 @@
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7.12</v>
+        <v>7.06</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.06</v>
+        <v>-15.1</v>
       </c>
       <c r="M9" t="n">
         <v>25.86</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.7</v>
+        <v>60.6</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
       </c>
       <c r="H10" t="n">
-        <v>65.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>26.7</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>11.79</v>
+        <v>11.67</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.289999999999999</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>46.3</v>
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="G11" t="n">
         <v>76</v>
       </c>
       <c r="H11" t="n">
-        <v>35.5</v>
+        <v>35.7</v>
       </c>
       <c r="I11" t="n">
         <v>61.9</v>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-1.37</v>
+        <v>-1.25</v>
       </c>
       <c r="L11" t="n">
-        <v>-18.38</v>
+        <v>-18.28</v>
       </c>
       <c r="M11" t="n">
         <v>26.55</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>51.8</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>33.4</v>
+        <v>33.8</v>
       </c>
       <c r="I13" t="n">
         <v>59.5</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.92</v>
+        <v>-11.7</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.26</v>
+        <v>-3.02</v>
       </c>
       <c r="M13" t="n">
-        <v>27.68</v>
+        <v>27.69</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.14</v>
+        <v>5.03</v>
       </c>
       <c r="L2" t="n">
-        <v>13.35</v>
+        <v>13.23</v>
       </c>
       <c r="M2" t="n">
         <v>11.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>94.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.51</v>
+        <v>6.31</v>
       </c>
       <c r="L3" t="n">
-        <v>28.98</v>
+        <v>28.73</v>
       </c>
       <c r="M3" t="n">
         <v>22.63</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.37</v>
+        <v>10.04</v>
       </c>
       <c r="L4" t="n">
-        <v>45.52</v>
+        <v>45.07</v>
       </c>
       <c r="M4" t="n">
-        <v>30.12</v>
+        <v>30.13</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>91.3</v>
+        <v>93.3</v>
       </c>
       <c r="I5" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-2.48</v>
+        <v>-1.6</v>
       </c>
       <c r="L5" t="n">
-        <v>51.84</v>
+        <v>53.22</v>
       </c>
       <c r="M5" t="n">
-        <v>38.92</v>
+        <v>38.99</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>89.3</v>
+        <v>89</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7.28</v>
+        <v>5.8</v>
       </c>
       <c r="L6" t="n">
-        <v>7.79</v>
+        <v>6.3</v>
       </c>
       <c r="M6" t="n">
-        <v>14.52</v>
+        <v>14.72</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>55.1</v>
+        <v>56.8</v>
       </c>
       <c r="I7" t="n">
         <v>95.3</v>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.91</v>
+        <v>-0.98</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.93</v>
+        <v>0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>11.39</v>
+        <v>11.4</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.71</v>
+        <v>-6.69</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>54.9</v>
+        <v>54.5</v>
       </c>
       <c r="I8" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.32</v>
+        <v>4.11</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.41</v>
+        <v>-0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>17.93</v>
+        <v>17.95</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>55.9</v>
+        <v>55.6</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7.06</v>
+        <v>6.88</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.1</v>
+        <v>-15.25</v>
       </c>
       <c r="M9" t="n">
-        <v>25.86</v>
+        <v>25.87</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.6</v>
+        <v>62.4</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
       </c>
       <c r="H10" t="n">
-        <v>65.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="I10" t="n">
         <v>26.7</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>11.67</v>
+        <v>14.62</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.380000000000001</v>
+        <v>-6.99</v>
       </c>
       <c r="M10" t="n">
-        <v>46.3</v>
+        <v>46.33</v>
       </c>
       <c r="N10" t="n">
         <v>-36.07</v>
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>59.8</v>
+        <v>60.1</v>
       </c>
       <c r="G11" t="n">
         <v>76</v>
       </c>
       <c r="H11" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="I11" t="n">
         <v>61.9</v>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-1.25</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-18.28</v>
+        <v>-17.82</v>
       </c>
       <c r="M11" t="n">
-        <v>26.55</v>
+        <v>26.54</v>
       </c>
       <c r="N11" t="n">
         <v>-25.29</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>53.1</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>33.8</v>
+        <v>37.2</v>
       </c>
       <c r="I13" t="n">
-        <v>59.5</v>
+        <v>59.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.7</v>
+        <v>-10.01</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.02</v>
+        <v>-1.16</v>
       </c>
       <c r="M13" t="n">
-        <v>27.69</v>
+        <v>27.87</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.3</v>
+        <v>78.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.03</v>
+        <v>2.57</v>
       </c>
       <c r="L2" t="n">
-        <v>13.23</v>
+        <v>13.39</v>
       </c>
       <c r="M2" t="n">
-        <v>11.55</v>
+        <v>11.57</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.5</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>93.7</v>
+        <v>89.2</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.31</v>
+        <v>2.75</v>
       </c>
       <c r="L3" t="n">
-        <v>28.73</v>
+        <v>28.38</v>
       </c>
       <c r="M3" t="n">
-        <v>22.63</v>
+        <v>22.65</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.04</v>
+        <v>10.2</v>
       </c>
       <c r="L4" t="n">
-        <v>45.07</v>
+        <v>44.7</v>
       </c>
       <c r="M4" t="n">
-        <v>30.13</v>
+        <v>30.12</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.2</v>
+        <v>79.7</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>93.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-1.6</v>
+        <v>-8.49</v>
       </c>
       <c r="L5" t="n">
-        <v>53.22</v>
+        <v>54.37</v>
       </c>
       <c r="M5" t="n">
-        <v>38.99</v>
+        <v>38.89</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>69.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>89</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.8</v>
+        <v>5.99</v>
       </c>
       <c r="L6" t="n">
-        <v>6.3</v>
+        <v>7.05</v>
       </c>
       <c r="M6" t="n">
-        <v>14.72</v>
+        <v>14.6</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>56.8</v>
+        <v>55.8</v>
       </c>
       <c r="I7" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="L7" t="n">
         <v>-0.98</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.02</v>
-      </c>
       <c r="M7" t="n">
-        <v>11.4</v>
+        <v>11.43</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.69</v>
+        <v>-6.82</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="I8" t="n">
         <v>77.2</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.11</v>
+        <v>4.61</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.61</v>
+        <v>-2.97</v>
       </c>
       <c r="M8" t="n">
-        <v>17.95</v>
+        <v>17.96</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63.2</v>
+        <v>61.9</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>55.6</v>
+        <v>51.7</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6.88</v>
+        <v>3.67</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.25</v>
+        <v>-15.23</v>
       </c>
       <c r="M9" t="n">
-        <v>25.87</v>
+        <v>25.86</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1381,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62.4</v>
+        <v>59.1</v>
       </c>
       <c r="G10" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>70.7</v>
+        <v>33.7</v>
       </c>
       <c r="I10" t="n">
-        <v>26.7</v>
+        <v>61.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,46 +1417,46 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>14.62</v>
+        <v>-2.98</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.99</v>
+        <v>-18.21</v>
       </c>
       <c r="M10" t="n">
-        <v>46.33</v>
+        <v>26.54</v>
       </c>
       <c r="N10" t="n">
-        <v>-36.07</v>
+        <v>-25.29</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF difesa/sicurezza UCITS</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>LMT|RTX|BA.L</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1486,35 +1486,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>60.1</v>
+        <v>58.9</v>
       </c>
       <c r="G11" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H11" t="n">
-        <v>36.7</v>
+        <v>60.4</v>
       </c>
       <c r="I11" t="n">
-        <v>61.9</v>
+        <v>26.7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1522,46 +1522,46 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-0.6899999999999999</v>
+        <v>10.45</v>
       </c>
       <c r="L11" t="n">
-        <v>-17.82</v>
+        <v>-14.56</v>
       </c>
       <c r="M11" t="n">
-        <v>26.54</v>
+        <v>46.29</v>
       </c>
       <c r="N11" t="n">
-        <v>-25.29</v>
+        <v>-36.07</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>LMT|RTX|BA.L</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>53.1</v>
+        <v>51.7</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>37.2</v>
+        <v>33</v>
       </c>
       <c r="I13" t="n">
-        <v>59.3</v>
+        <v>59.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.01</v>
+        <v>-12.88</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.16</v>
+        <v>-2.18</v>
       </c>
       <c r="M13" t="n">
-        <v>27.87</v>
+        <v>27.72</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.5</v>
+        <v>89.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.5</v>
+        <v>78</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="L2" t="n">
-        <v>13.39</v>
+        <v>13.11</v>
       </c>
       <c r="M2" t="n">
-        <v>11.57</v>
+        <v>11.59</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>85.2</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>89.2</v>
+        <v>89.8</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="L3" t="n">
-        <v>28.38</v>
+        <v>28.73</v>
       </c>
       <c r="M3" t="n">
-        <v>22.65</v>
+        <v>22.63</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.2</v>
+        <v>11.11</v>
       </c>
       <c r="L4" t="n">
-        <v>44.7</v>
+        <v>45.89</v>
       </c>
       <c r="M4" t="n">
-        <v>30.12</v>
+        <v>30.11</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>85.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>46.1</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-8.49</v>
+        <v>-7.43</v>
       </c>
       <c r="L5" t="n">
-        <v>54.37</v>
+        <v>56.17</v>
       </c>
       <c r="M5" t="n">
-        <v>38.89</v>
+        <v>38.9</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>70.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.99</v>
+        <v>5.61</v>
       </c>
       <c r="L6" t="n">
-        <v>7.05</v>
+        <v>6.66</v>
       </c>
       <c r="M6" t="n">
-        <v>14.6</v>
+        <v>14.65</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>55.8</v>
+        <v>54</v>
       </c>
       <c r="I7" t="n">
         <v>95.2</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.3</v>
+        <v>-2.23</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.98</v>
+        <v>-1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>11.43</v>
+        <v>11.39</v>
       </c>
       <c r="N7" t="n">
         <v>-6.82</v>
@@ -1200,7 +1200,7 @@
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>53.5</v>
+        <v>53.3</v>
       </c>
       <c r="I8" t="n">
         <v>77.2</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.97</v>
+        <v>-3.04</v>
       </c>
       <c r="M8" t="n">
         <v>17.96</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>51.7</v>
+        <v>52.1</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.67</v>
+        <v>3.87</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.23</v>
+        <v>-15.07</v>
       </c>
       <c r="M9" t="n">
         <v>25.86</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.1</v>
+        <v>58.6</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.7</v>
+        <v>32.4</v>
       </c>
       <c r="I10" t="n">
         <v>61.9</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-2.98</v>
+        <v>-3.68</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.21</v>
+        <v>-18.8</v>
       </c>
       <c r="M10" t="n">
-        <v>26.54</v>
+        <v>26.55</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1505,16 +1505,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>58.9</v>
+        <v>58.3</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
       </c>
       <c r="H11" t="n">
-        <v>60.4</v>
+        <v>58.4</v>
       </c>
       <c r="I11" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>10.45</v>
+        <v>9.32</v>
       </c>
       <c r="L11" t="n">
-        <v>-14.56</v>
+        <v>-15.43</v>
       </c>
       <c r="M11" t="n">
-        <v>46.29</v>
+        <v>46.28</v>
       </c>
       <c r="N11" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>51.7</v>
+        <v>50.6</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>33</v>
+        <v>29.8</v>
       </c>
       <c r="I13" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.88</v>
+        <v>-14.48</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.18</v>
+        <v>-3.97</v>
       </c>
       <c r="M13" t="n">
-        <v>27.72</v>
+        <v>27.66</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,27 +568,27 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.31</v>
+        <v>0.78</v>
       </c>
       <c r="L2" t="n">
-        <v>13.11</v>
+        <v>13.01</v>
       </c>
       <c r="M2" t="n">
         <v>11.59</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.2</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>89.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.04</v>
+        <v>0.05</v>
       </c>
       <c r="L3" t="n">
-        <v>28.73</v>
+        <v>29.09</v>
       </c>
       <c r="M3" t="n">
-        <v>22.63</v>
+        <v>22.56</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>60.4</v>
+        <v>60.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.11</v>
+        <v>9.83</v>
       </c>
       <c r="L4" t="n">
-        <v>45.89</v>
+        <v>45.83</v>
       </c>
       <c r="M4" t="n">
-        <v>30.11</v>
+        <v>30.16</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>80.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>88.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="I5" t="n">
         <v>46.1</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-7.43</v>
+        <v>-11.52</v>
       </c>
       <c r="L5" t="n">
-        <v>56.17</v>
+        <v>54.05</v>
       </c>
       <c r="M5" t="n">
-        <v>38.9</v>
+        <v>38.95</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>69.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="I6" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.61</v>
+        <v>6.65</v>
       </c>
       <c r="L6" t="n">
-        <v>6.66</v>
+        <v>6.51</v>
       </c>
       <c r="M6" t="n">
-        <v>14.65</v>
+        <v>14.58</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>71.2</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="I7" t="n">
         <v>95.2</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.23</v>
+        <v>-1.51</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.92</v>
+        <v>-2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>11.39</v>
+        <v>11.49</v>
       </c>
       <c r="N7" t="n">
         <v>-6.82</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="I8" t="n">
         <v>77.2</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.54</v>
+        <v>0.75</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.04</v>
+        <v>-1.34</v>
       </c>
       <c r="M8" t="n">
-        <v>17.96</v>
+        <v>17.95</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>60.6</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>52.1</v>
+        <v>48.1</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.87</v>
+        <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.07</v>
+        <v>-14.67</v>
       </c>
       <c r="M9" t="n">
-        <v>25.86</v>
+        <v>25.87</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="I10" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-3.68</v>
+        <v>-4.69</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.8</v>
+        <v>-16.86</v>
       </c>
       <c r="M10" t="n">
-        <v>26.55</v>
+        <v>26.49</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Obbligazionario Globale</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1505,83 +1505,71 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>58.3</v>
+        <v>57.7</v>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H11" t="n">
-        <v>58.4</v>
+        <v>50</v>
       </c>
       <c r="I11" t="n">
-        <v>26.8</v>
+        <v>50</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-15.43</v>
-      </c>
-      <c r="M11" t="n">
-        <v>46.28</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-36.07</v>
-      </c>
+          <t>Dati limitati</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF obbligazionario</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>EUNA.MI</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
-        </is>
-      </c>
+          <t>ETF global aggregate bond hedged/unhedged</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>9-35%</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Lungo periodo</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Rischio tassi cambio e duration</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Da allineare a orizzonte e consulenza Fineco</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Obbligazionario Globale</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1610,71 +1598,83 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>57.7</v>
+        <v>56.4</v>
       </c>
       <c r="G12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>26.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Dati limitati</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Debole o laterale</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-14.27</v>
+      </c>
+      <c r="M12" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-36.07</v>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF obbligazionario</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>EUNA.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF global aggregate bond hedged/unhedged</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+          <t>ETF uranium/energy transition o fondo energia</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>CCJ|SHEL.L|ENI.MI</t>
+        </is>
+      </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>9-35%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Lungo periodo</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Rischio tassi cambio e duration</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Da allineare a orizzonte e consulenza Fineco</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>29.8</v>
+        <v>29.3</v>
       </c>
       <c r="I13" t="n">
-        <v>59.6</v>
+        <v>59.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-14.48</v>
+        <v>-14.84</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.97</v>
+        <v>-4.11</v>
       </c>
       <c r="M13" t="n">
-        <v>27.66</v>
+        <v>27.83</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>85.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>68</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.78</v>
+        <v>0.21</v>
       </c>
       <c r="L2" t="n">
-        <v>13.01</v>
+        <v>12.37</v>
       </c>
       <c r="M2" t="n">
-        <v>11.59</v>
+        <v>11.66</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>86.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="I3" t="n">
         <v>74.3</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.05</v>
+        <v>-0.55</v>
       </c>
       <c r="L3" t="n">
-        <v>29.09</v>
+        <v>28.32</v>
       </c>
       <c r="M3" t="n">
-        <v>22.56</v>
+        <v>22.6</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.83</v>
+        <v>10.48</v>
       </c>
       <c r="L4" t="n">
-        <v>45.83</v>
+        <v>46.7</v>
       </c>
       <c r="M4" t="n">
-        <v>30.16</v>
+        <v>30.19</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -865,30 +865,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>78.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I5" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-11.52</v>
+        <v>-12.75</v>
       </c>
       <c r="L5" t="n">
-        <v>54.05</v>
+        <v>51.91</v>
       </c>
       <c r="M5" t="n">
-        <v>38.95</v>
+        <v>39.04</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>70.5</v>
+        <v>69.5</v>
       </c>
       <c r="I6" t="n">
-        <v>89.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.65</v>
+        <v>6.1</v>
       </c>
       <c r="L6" t="n">
-        <v>6.51</v>
+        <v>5.96</v>
       </c>
       <c r="M6" t="n">
-        <v>14.58</v>
+        <v>14.6</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>54.5</v>
+        <v>54.3</v>
       </c>
       <c r="I7" t="n">
         <v>95.2</v>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.51</v>
+        <v>-1.61</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.35</v>
+        <v>-2.46</v>
       </c>
       <c r="M7" t="n">
-        <v>11.49</v>
+        <v>11.5</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.82</v>
+        <v>-6.89</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65.5</v>
+        <v>65</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>48.6</v>
       </c>
       <c r="I8" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.34</v>
+        <v>-2.07</v>
       </c>
       <c r="M8" t="n">
-        <v>17.95</v>
+        <v>18.02</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.6</v>
+        <v>60.4</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>48.1</v>
+        <v>47.5</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.35</v>
+        <v>-0.01</v>
       </c>
       <c r="L9" t="n">
-        <v>-14.67</v>
+        <v>-14.97</v>
       </c>
       <c r="M9" t="n">
-        <v>25.87</v>
+        <v>25.88</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>32.6</v>
+        <v>32.2</v>
       </c>
       <c r="I10" t="n">
         <v>62</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.69</v>
+        <v>-4.9</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.86</v>
+        <v>-17.04</v>
       </c>
       <c r="M10" t="n">
-        <v>26.49</v>
+        <v>26.51</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56.4</v>
+        <v>55.7</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I12" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>4.14</v>
+        <v>3.05</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.27</v>
+        <v>-15.17</v>
       </c>
       <c r="M12" t="n">
-        <v>46.52</v>
+        <v>46.62</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>29.3</v>
+        <v>27.5</v>
       </c>
       <c r="I13" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-14.84</v>
+        <v>-15.76</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.11</v>
+        <v>-5.14</v>
       </c>
       <c r="M13" t="n">
-        <v>27.83</v>
+        <v>27.95</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>85.5</v>
+        <v>85.7</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>66.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="L2" t="n">
-        <v>12.37</v>
+        <v>12.59</v>
       </c>
       <c r="M2" t="n">
-        <v>11.66</v>
+        <v>11.63</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>85.2</v>
+        <v>86.3</v>
       </c>
       <c r="I3" t="n">
         <v>74.3</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>28.32</v>
+        <v>29.03</v>
       </c>
       <c r="M3" t="n">
-        <v>22.6</v>
+        <v>22.56</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.48</v>
+        <v>10.98</v>
       </c>
       <c r="L4" t="n">
-        <v>46.7</v>
+        <v>47.36</v>
       </c>
       <c r="M4" t="n">
-        <v>30.19</v>
+        <v>30.22</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>79</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-12.75</v>
+        <v>-12.11</v>
       </c>
       <c r="L5" t="n">
-        <v>51.91</v>
+        <v>53.03</v>
       </c>
       <c r="M5" t="n">
-        <v>39.04</v>
+        <v>38.98</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>69.5</v>
+        <v>69</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.1</v>
+        <v>5.84</v>
       </c>
       <c r="L6" t="n">
-        <v>5.96</v>
+        <v>5.7</v>
       </c>
       <c r="M6" t="n">
-        <v>14.6</v>
+        <v>14.61</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>54.3</v>
+        <v>53.3</v>
       </c>
       <c r="I7" t="n">
-        <v>95.2</v>
+        <v>94.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.61</v>
+        <v>-2.15</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.46</v>
+        <v>-2.99</v>
       </c>
       <c r="M7" t="n">
-        <v>11.5</v>
+        <v>11.57</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.89</v>
+        <v>-7.4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="I8" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.07</v>
+        <v>-1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>18.02</v>
+        <v>18.01</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>47.5</v>
+        <v>47.8</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-0.01</v>
+        <v>0.13</v>
       </c>
       <c r="L9" t="n">
-        <v>-14.97</v>
+        <v>-14.85</v>
       </c>
       <c r="M9" t="n">
-        <v>25.88</v>
+        <v>25.87</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>32.2</v>
+        <v>32.6</v>
       </c>
       <c r="I10" t="n">
         <v>62</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.9</v>
+        <v>-4.66</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.04</v>
+        <v>-16.83</v>
       </c>
       <c r="M10" t="n">
-        <v>26.51</v>
+        <v>26.49</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="I12" t="n">
         <v>26.3</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="L12" t="n">
-        <v>-15.17</v>
+        <v>-15.04</v>
       </c>
       <c r="M12" t="n">
-        <v>46.62</v>
+        <v>46.6</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.8</v>
+        <v>50.3</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>27.5</v>
+        <v>28.9</v>
       </c>
       <c r="I13" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-15.76</v>
+        <v>-15.05</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.14</v>
+        <v>-4.34</v>
       </c>
       <c r="M13" t="n">
-        <v>27.95</v>
+        <v>27.85</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,30 +568,30 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>85.7</v>
+        <v>88.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>67.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="L2" t="n">
-        <v>12.59</v>
+        <v>12.89</v>
       </c>
       <c r="M2" t="n">
-        <v>11.63</v>
+        <v>11.56</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>84.7</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>86.3</v>
+        <v>88.3</v>
       </c>
       <c r="I3" t="n">
         <v>74.3</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="L3" t="n">
-        <v>29.03</v>
+        <v>28.71</v>
       </c>
       <c r="M3" t="n">
-        <v>22.56</v>
+        <v>22.54</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.98</v>
+        <v>9.1</v>
       </c>
       <c r="L4" t="n">
-        <v>47.36</v>
+        <v>45.36</v>
       </c>
       <c r="M4" t="n">
-        <v>30.22</v>
+        <v>30.16</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -865,30 +865,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>77.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>80.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-12.11</v>
+        <v>-9.41</v>
       </c>
       <c r="L5" t="n">
-        <v>53.03</v>
+        <v>51.32</v>
       </c>
       <c r="M5" t="n">
-        <v>38.98</v>
+        <v>38.93</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>69</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.84</v>
+        <v>6.92</v>
       </c>
       <c r="L6" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>14.61</v>
+        <v>14.54</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>70.7</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>53.3</v>
+        <v>53.9</v>
       </c>
       <c r="I7" t="n">
-        <v>94.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.15</v>
+        <v>-1.94</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.99</v>
+        <v>-2.53</v>
       </c>
       <c r="M7" t="n">
-        <v>11.57</v>
+        <v>11.47</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.4</v>
+        <v>-7.04</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>48.8</v>
+        <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.12</v>
+        <v>-1.5</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.95</v>
+        <v>-0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>18.01</v>
+        <v>17.93</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.5</v>
+        <v>60.8</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>47.8</v>
+        <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="L9" t="n">
-        <v>-14.85</v>
+        <v>-13.81</v>
       </c>
       <c r="M9" t="n">
-        <v>25.87</v>
+        <v>25.89</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.7</v>
+        <v>59.3</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>32.6</v>
+        <v>34.2</v>
       </c>
       <c r="I10" t="n">
-        <v>62</v>
+        <v>62.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.66</v>
+        <v>-3.07</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.83</v>
+        <v>-17.33</v>
       </c>
       <c r="M10" t="n">
-        <v>26.49</v>
+        <v>26.36</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.8</v>
+        <v>52.6</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>51.3</v>
+        <v>42</v>
       </c>
       <c r="I12" t="n">
         <v>26.3</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3.21</v>
+        <v>-4.06</v>
       </c>
       <c r="L12" t="n">
-        <v>-15.04</v>
+        <v>-15.93</v>
       </c>
       <c r="M12" t="n">
         <v>46.6</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>28.9</v>
+        <v>29.7</v>
       </c>
       <c r="I13" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-15.05</v>
+        <v>-14.92</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.34</v>
+        <v>-3.42</v>
       </c>
       <c r="M13" t="n">
-        <v>27.85</v>
+        <v>27.77</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.8</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>76.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="L2" t="n">
-        <v>12.89</v>
+        <v>13.1</v>
       </c>
       <c r="M2" t="n">
         <v>11.56</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.7</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>88.3</v>
+        <v>89.3</v>
       </c>
       <c r="I3" t="n">
         <v>74.3</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="L3" t="n">
-        <v>28.71</v>
+        <v>29.28</v>
       </c>
       <c r="M3" t="n">
         <v>22.54</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I4" t="n">
         <v>60.3</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.1</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>45.36</v>
+        <v>44.83</v>
       </c>
       <c r="M4" t="n">
         <v>30.16</v>
@@ -885,7 +885,7 @@
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="I5" t="n">
         <v>46.1</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-9.41</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>51.32</v>
+        <v>51.22</v>
       </c>
       <c r="M5" t="n">
         <v>38.93</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>70.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.92</v>
+        <v>6.21</v>
       </c>
       <c r="L6" t="n">
-        <v>6.6</v>
+        <v>5.89</v>
       </c>
       <c r="M6" t="n">
-        <v>14.54</v>
+        <v>14.55</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>70.7</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>53.9</v>
+        <v>53.3</v>
       </c>
       <c r="I7" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.94</v>
+        <v>-2.24</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.53</v>
+        <v>-2.83</v>
       </c>
       <c r="M7" t="n">
-        <v>11.47</v>
+        <v>11.48</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.04</v>
+        <v>-7.33</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I8" t="n">
         <v>77.3</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.5</v>
+        <v>-1.55</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>17.93</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.8</v>
+        <v>61.5</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>48.6</v>
+        <v>50.6</v>
       </c>
       <c r="I9" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.21</v>
+        <v>1.32</v>
       </c>
       <c r="L9" t="n">
-        <v>-13.81</v>
+        <v>-12.87</v>
       </c>
       <c r="M9" t="n">
-        <v>25.89</v>
+        <v>25.86</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.3</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-3.07</v>
+        <v>-3.63</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.33</v>
+        <v>-17.8</v>
       </c>
       <c r="M10" t="n">
         <v>26.36</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.6</v>
+        <v>52.2</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>42</v>
+        <v>40.8</v>
       </c>
       <c r="I12" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.06</v>
+        <v>-4.68</v>
       </c>
       <c r="L12" t="n">
-        <v>-15.93</v>
+        <v>-16.48</v>
       </c>
       <c r="M12" t="n">
-        <v>46.6</v>
+        <v>46.66</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>29.7</v>
+        <v>30.4</v>
       </c>
       <c r="I13" t="n">
         <v>59.4</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-14.92</v>
+        <v>-14.55</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.42</v>
+        <v>-3</v>
       </c>
       <c r="M13" t="n">
         <v>27.77</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77</v>
+        <v>77.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="L2" t="n">
-        <v>13.1</v>
+        <v>13.22</v>
       </c>
       <c r="M2" t="n">
         <v>11.56</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>85.2</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>89.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>74.3</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="L3" t="n">
-        <v>29.28</v>
+        <v>29.68</v>
       </c>
       <c r="M3" t="n">
-        <v>22.54</v>
+        <v>22.55</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.2</v>
+        <v>82.7</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>99.8</v>
+        <v>98.5</v>
       </c>
       <c r="I4" t="n">
         <v>60.3</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8.710000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="L4" t="n">
-        <v>44.83</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>30.16</v>
+        <v>30.17</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>78.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>82.5</v>
+        <v>84.3</v>
       </c>
       <c r="I5" t="n">
         <v>46.1</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-9.470000000000001</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>51.22</v>
+        <v>52.5</v>
       </c>
       <c r="M5" t="n">
-        <v>38.93</v>
+        <v>38.91</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>69.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.21</v>
+        <v>5.83</v>
       </c>
       <c r="L6" t="n">
-        <v>5.89</v>
+        <v>5.51</v>
       </c>
       <c r="M6" t="n">
-        <v>14.55</v>
+        <v>14.57</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.24</v>
+        <v>-2.26</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.83</v>
+        <v>-2.86</v>
       </c>
       <c r="M7" t="n">
         <v>11.48</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.33</v>
+        <v>-7.36</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="I8" t="n">
         <v>77.3</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.55</v>
+        <v>-1.42</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>17.93</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.5</v>
+        <v>61.3</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="L9" t="n">
-        <v>-12.87</v>
+        <v>-13.07</v>
       </c>
       <c r="M9" t="n">
         <v>25.86</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>58.8</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-3.63</v>
+        <v>-3.87</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.8</v>
+        <v>-18.01</v>
       </c>
       <c r="M10" t="n">
         <v>26.36</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.2</v>
+        <v>51.5</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>40.8</v>
+        <v>38.9</v>
       </c>
       <c r="I12" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.68</v>
+        <v>-5.76</v>
       </c>
       <c r="L12" t="n">
-        <v>-16.48</v>
+        <v>-17.42</v>
       </c>
       <c r="M12" t="n">
-        <v>46.66</v>
+        <v>46.78</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="I13" t="n">
         <v>59.4</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-14.55</v>
+        <v>-14.4</v>
       </c>
       <c r="L13" t="n">
-        <v>-3</v>
+        <v>-2.83</v>
       </c>
       <c r="M13" t="n">
-        <v>27.77</v>
+        <v>27.78</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>
